--- a/cds_files/Clemson_CDS_2021-2022.xlsx
+++ b/cds_files/Clemson_CDS_2021-2022.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02</v>
+        <v>0.33</v>
       </c>
       <c r="C3" t="n">
         <v>0.33</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02</v>
+        <v>0.59</v>
       </c>
       <c r="C4" t="n">
         <v>0.59</v>
